--- a/formulasi_susu_ibu_hamil_kompleks.xlsx
+++ b/formulasi_susu_ibu_hamil_kompleks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/awp/Documents/R-Studio/Praktikum Uji Sensoris/formulasi-fortifikasi-gizi/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A28CAA04-BE3C-1143-BD2E-599E52A670C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{944DA7B0-5679-BE43-B444-88FA8174AFB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,9 +23,10 @@
     <definedName name="solver_lhs1" localSheetId="0" hidden="1">Formulasi!$B$19:$B$31</definedName>
     <definedName name="solver_lhs2" localSheetId="0" hidden="1">Formulasi!$B$19:$B$31</definedName>
     <definedName name="solver_lhs3" localSheetId="0" hidden="1">Formulasi!$B$32</definedName>
-    <definedName name="solver_lhs4" localSheetId="0" hidden="1">Formulasi!$B$44:$B$47</definedName>
-    <definedName name="solver_lhs5" localSheetId="0" hidden="1">Formulasi!$C$32:$N$32</definedName>
-    <definedName name="solver_lhs6" localSheetId="0" hidden="1">Formulasi!$C$32:$N$32</definedName>
+    <definedName name="solver_lhs4" localSheetId="0" hidden="1">Formulasi!$B$32:$N$32</definedName>
+    <definedName name="solver_lhs5" localSheetId="0" hidden="1">Formulasi!$B$32:$N$32</definedName>
+    <definedName name="solver_lhs6" localSheetId="0" hidden="1">Formulasi!$B$44:$B$47</definedName>
+    <definedName name="solver_lhs7" localSheetId="0" hidden="1">Formulasi!$E$32</definedName>
     <definedName name="solver_lin" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_mni" localSheetId="0" hidden="1">30</definedName>
@@ -34,21 +35,23 @@
     <definedName name="solver_neg" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_num" localSheetId="0" hidden="1">0</definedName>
-    <definedName name="solver_opt" localSheetId="0" hidden="1">Formulasi!$F$58</definedName>
+    <definedName name="solver_opt" localSheetId="0" hidden="1">Formulasi!$B$31</definedName>
     <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
     <definedName name="solver_rbv" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rel2" localSheetId="0" hidden="1">3</definedName>
     <definedName name="solver_rel3" localSheetId="0" hidden="1">2</definedName>
-    <definedName name="solver_rel4" localSheetId="0" hidden="1">3</definedName>
-    <definedName name="solver_rel5" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rel4" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rel5" localSheetId="0" hidden="1">3</definedName>
     <definedName name="solver_rel6" localSheetId="0" hidden="1">3</definedName>
+    <definedName name="solver_rel7" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_rhs1" localSheetId="0" hidden="1">Formulasi!$P$19:$P$31</definedName>
     <definedName name="solver_rhs2" localSheetId="0" hidden="1">Formulasi!$O$19:$O$31</definedName>
     <definedName name="solver_rhs3" localSheetId="0" hidden="1">100</definedName>
-    <definedName name="solver_rhs4" localSheetId="0" hidden="1">0</definedName>
-    <definedName name="solver_rhs5" localSheetId="0" hidden="1">Formulasi!$C$35:$N$35</definedName>
-    <definedName name="solver_rhs6" localSheetId="0" hidden="1">Formulasi!$C$34:$N$34</definedName>
+    <definedName name="solver_rhs4" localSheetId="0" hidden="1">Formulasi!$B$35:$N$35</definedName>
+    <definedName name="solver_rhs5" localSheetId="0" hidden="1">Formulasi!$B$34:$N$34</definedName>
+    <definedName name="solver_rhs6" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_rhs7" localSheetId="0" hidden="1">9</definedName>
     <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_rsd" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_scl" localSheetId="0" hidden="1">1</definedName>
@@ -1333,7 +1336,9 @@
         <f t="shared" ref="A19:A31" si="1">A3</f>
         <v>Susu skim bubuk</v>
       </c>
-      <c r="B19" s="7"/>
+      <c r="B19" s="7">
+        <v>0</v>
+      </c>
       <c r="C19" s="8">
         <f t="shared" ref="C19:N19" si="2">$B19/100*B3</f>
         <v>0</v>
@@ -1394,7 +1399,9 @@
         <f t="shared" si="1"/>
         <v>Susu full cream bubuk</v>
       </c>
-      <c r="B20" s="7"/>
+      <c r="B20" s="7">
+        <v>0</v>
+      </c>
       <c r="C20" s="8">
         <f t="shared" ref="C20:N20" si="3">$B20/100*B4</f>
         <v>0</v>
@@ -1455,7 +1462,9 @@
         <f t="shared" si="1"/>
         <v>Whey protein concentrate (WPC80)</v>
       </c>
-      <c r="B21" s="7"/>
+      <c r="B21" s="7">
+        <v>0</v>
+      </c>
       <c r="C21" s="8">
         <f t="shared" ref="C21:N21" si="4">$B21/100*B5</f>
         <v>0</v>
@@ -1516,7 +1525,9 @@
         <f t="shared" si="1"/>
         <v>Isolat protein kedelai</v>
       </c>
-      <c r="B22" s="7"/>
+      <c r="B22" s="7">
+        <v>0</v>
+      </c>
       <c r="C22" s="8">
         <f t="shared" ref="C22:N22" si="5">$B22/100*B6</f>
         <v>0</v>
@@ -1577,7 +1588,9 @@
         <f t="shared" si="1"/>
         <v>Maltodekstrin</v>
       </c>
-      <c r="B23" s="7"/>
+      <c r="B23" s="7">
+        <v>0</v>
+      </c>
       <c r="C23" s="8">
         <f t="shared" ref="C23:N23" si="6">$B23/100*B7</f>
         <v>0</v>
@@ -1638,7 +1651,9 @@
         <f t="shared" si="1"/>
         <v>Gula pasir (sukrosa)</v>
       </c>
-      <c r="B24" s="7"/>
+      <c r="B24" s="7">
+        <v>0</v>
+      </c>
       <c r="C24" s="8">
         <f t="shared" ref="C24:N24" si="7">$B24/100*B8</f>
         <v>0</v>
@@ -1699,7 +1714,9 @@
         <f t="shared" si="1"/>
         <v>Bubuk lemak nabati (70% lemak)</v>
       </c>
-      <c r="B25" s="7"/>
+      <c r="B25" s="7">
+        <v>0</v>
+      </c>
       <c r="C25" s="8">
         <f t="shared" ref="C25:N25" si="8">$B25/100*B9</f>
         <v>0</v>
@@ -1760,7 +1777,9 @@
         <f t="shared" si="1"/>
         <v>Bubuk DHA (10% DHA)</v>
       </c>
-      <c r="B26" s="7"/>
+      <c r="B26" s="7">
+        <v>0</v>
+      </c>
       <c r="C26" s="8">
         <f t="shared" ref="C26:N26" si="9">$B26/100*B10</f>
         <v>0</v>
@@ -1821,7 +1840,9 @@
         <f t="shared" si="1"/>
         <v>FOS-inulin</v>
       </c>
-      <c r="B27" s="7"/>
+      <c r="B27" s="7">
+        <v>0</v>
+      </c>
       <c r="C27" s="8">
         <f t="shared" ref="C27:N27" si="10">$B27/100*B11</f>
         <v>0</v>
@@ -1882,7 +1903,9 @@
         <f t="shared" si="1"/>
         <v>Kakao bubuk</v>
       </c>
-      <c r="B28" s="7"/>
+      <c r="B28" s="7">
+        <v>0</v>
+      </c>
       <c r="C28" s="8">
         <f t="shared" ref="C28:N28" si="11">$B28/100*B12</f>
         <v>0</v>
@@ -1943,7 +1966,9 @@
         <f t="shared" si="1"/>
         <v>Kalsium karbonat</v>
       </c>
-      <c r="B29" s="7"/>
+      <c r="B29" s="7">
+        <v>0</v>
+      </c>
       <c r="C29" s="8">
         <f t="shared" ref="C29:N29" si="12">$B29/100*B13</f>
         <v>0</v>
@@ -2004,7 +2029,9 @@
         <f t="shared" si="1"/>
         <v>Trikalsium fosfat</v>
       </c>
-      <c r="B30" s="7"/>
+      <c r="B30" s="7">
+        <v>0</v>
+      </c>
       <c r="C30" s="8">
         <f t="shared" ref="C30:N30" si="13">$B30/100*B14</f>
         <v>0</v>
@@ -2065,7 +2092,9 @@
         <f t="shared" si="1"/>
         <v>Premix vitamin-mineral</v>
       </c>
-      <c r="B31" s="9"/>
+      <c r="B31" s="9">
+        <v>0</v>
+      </c>
       <c r="C31" s="8">
         <f t="shared" ref="C31:N31" si="14">$B31/100*B15</f>
         <v>0</v>
@@ -2189,10 +2218,10 @@
         <v>0</v>
       </c>
       <c r="D34" s="4">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E34" s="4">
-        <v>8</v>
+        <v>3.5</v>
       </c>
       <c r="F34" s="4">
         <v>0</v>
@@ -2204,7 +2233,7 @@
         <v>3</v>
       </c>
       <c r="I34" s="4">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="J34" s="4">
         <v>600</v>
@@ -2219,7 +2248,7 @@
         <v>100</v>
       </c>
       <c r="N34" s="4">
-        <v>380</v>
+        <v>325</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
@@ -2230,16 +2259,16 @@
         <v>100</v>
       </c>
       <c r="C35" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D35" s="4">
         <v>25</v>
       </c>
       <c r="E35" s="4">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F35" s="4">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G35" s="4">
         <v>10</v>
@@ -2248,13 +2277,13 @@
         <v>6</v>
       </c>
       <c r="I35" s="4">
-        <v>1400</v>
+        <v>950</v>
       </c>
       <c r="J35" s="4">
         <v>1000</v>
       </c>
       <c r="K35" s="4">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="L35" s="4">
         <v>500</v>
@@ -2263,7 +2292,7 @@
         <v>300</v>
       </c>
       <c r="N35" s="4">
-        <v>450</v>
+        <v>500</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.2">
